--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="포인트 경제" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아이템 가격" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보상·토스 지급" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보상·냥코인" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신규 지급" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출석" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="튜토리얼" sheetId="8" state="visible" r:id="rId8"/>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="10" min="1" max="1"/>
@@ -527,6 +527,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -575,11 +576,11 @@
     <row r="7" ht="17.15" customHeight="1" s="11">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>1인 최대 토스 지급(원)</t>
+          <t>1인 최대 냥코인 적립(=토스포인트 원)</t>
         </is>
       </c>
       <c r="B7" s="10">
-        <f>'보상·토스 지급'!D10</f>
+        <f>'보상·냥코인'!D10</f>
         <v/>
       </c>
     </row>
@@ -638,7 +639,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>'보상·토스 지급' 시트 노란 칸에 앱인토스 대시보드 값 입력</t>
+          <t>'보상·냥코인' 시트 노란 칸에 앱인토스 대시보드 값 입력</t>
         </is>
       </c>
     </row>
@@ -649,7 +650,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>'보상·토스 지급'!B23</f>
+        <f>'보상·냥코인'!B23</f>
         <v/>
       </c>
     </row>
@@ -666,14 +667,26 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>출석</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>1주차 출석 한정 아이템 7개 → 이후 주간 반복(10/10/15/15/20/20P + 7일차 상자/확률업 뽑기권 번갈아), 30·100일 기념 벽장식+배지, 리셋 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>냥코인</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>도감 보상으로만 적립, 1냥코인 = 토스포인트 1원, 10냥코인 단위로 토스포인트로 받기(서버 검증)</t>
         </is>
       </c>
     </row>
@@ -706,6 +719,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -776,6 +790,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="17.15" customHeight="1" s="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
@@ -803,6 +818,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="11">
       <c r="A14" s="18" t="inlineStr">
         <is>
@@ -865,6 +881,7 @@
         <v>150</v>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="17.15" customHeight="1" s="11">
       <c r="A21" s="18" t="inlineStr">
         <is>
@@ -1078,6 +1095,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="17.15" customHeight="1" s="11">
       <c r="A33" s="13" t="inlineStr">
         <is>
@@ -1108,7 +1126,7 @@
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>누적 토스 지급(원)</t>
+          <t>누적 냥코인 적립</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -1955,6 +1973,7 @@
         <v/>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -8197,6 +8216,7 @@
         </is>
       </c>
     </row>
+    <row r="148"/>
     <row r="149" ht="15" customHeight="1" s="11">
       <c r="A149" s="18" t="inlineStr">
         <is>
@@ -8397,6 +8417,7 @@
         <v/>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -8535,6 +8556,10 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12" ht="17.15" customHeight="1" s="11">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -8642,6 +8667,7 @@
         <v>400</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="17.15" customHeight="1" s="11">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -8669,7 +8695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="48" customWidth="1" style="10" min="1" max="1"/>
@@ -8683,10 +8709,11 @@
     <row r="1" ht="20.1" customHeight="1" s="11">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>토스 지급 (1인 최대)</t>
-        </is>
-      </c>
-    </row>
+          <t>냥코인 적립 (1인 최대) · 1냥코인 = 토스포인트 1원</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -8700,12 +8727,12 @@
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>토스(원)</t>
+          <t>냥코인</t>
         </is>
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
-          <t>토스 합계</t>
+          <t>냥코인 합계</t>
         </is>
       </c>
       <c r="E3" s="18" t="inlineStr">
@@ -8881,7 +8908,7 @@
     <row r="11" ht="17.15" customHeight="1" s="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>검증 (417원이어야 해요)</t>
+          <t>검증 (417냥코인이어야 해요)</t>
         </is>
       </c>
       <c r="D11" s="10">
@@ -8889,6 +8916,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="16.15" customHeight="1" s="11">
       <c r="A13" s="16" t="inlineStr">
         <is>
@@ -8955,13 +8983,14 @@
     <row r="19" ht="17.15" customHeight="1" s="11">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>기간 내 1인 토스 지급(원, 시뮬 30일 중앙값)</t>
+          <t>기간 내 1인 냥코인 적립(=토스포인트 원, 시뮬 30일 중앙값)</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
         <v>83</v>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="17.15" customHeight="1" s="11">
       <c r="A21" s="14" t="inlineStr">
         <is>
@@ -8976,7 +9005,7 @@
     <row r="22" ht="17.15" customHeight="1" s="11">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>1인 순이익(원) = 광고 수익 − 토스 지급</t>
+          <t>1인 순이익(원) = 광고 수익 − 토스포인트 지급</t>
         </is>
       </c>
       <c r="B22" s="10">
@@ -9009,11 +9038,121 @@
     <row r="25" ht="17.15" customHeight="1" s="11">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>최대 지급 417원 회수에 필요한 광고 수 (평균 eCPM 입력 시)</t>
+          <t>최대 적립 417냥코인 회수에 필요한 광고 수 (평균 eCPM 입력 시)</t>
         </is>
       </c>
       <c r="B25" s="10">
         <f>IF(B14="","eCPM 입력 필요",417*1000/B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>토스포인트로 받기 (출금 규칙)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>출금 단위</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>최소 출금</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>1회 최대</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>floor(잔액/10)×10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>남는 냥코인</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>그대로 보유 (예: 37 → 30 받고 7 남음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>서버: 10의 배수 · 10 이상 · 잔액 이하 · 계정당 동시 1건</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>멱등키</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>tossUserKey + withdrawRequestId</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>지급</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>서버→서버 토스 포인트 지급 API 호출, 실패 시 잔액 복구</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>지급 API 금액 한도·예산 충전·정책은 앱인토스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>최대 적립 417 중 출금 가능</t>
+        </is>
+      </c>
+      <c r="B36" s="14">
+        <f>FLOOR(D10/10,1)*10</f>
         <v/>
       </c>
     </row>
@@ -9047,6 +9186,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -9414,7 +9554,7 @@
       <c r="F15" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -9447,7 +9587,7 @@
       <c r="F16" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>출석 아이템은 가격 없음(구매 불가) → 가격 환산 합계에서 제외</t>
         </is>
@@ -9669,12 +9809,12 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>누적 출석일 기준 · 빠져도 리셋 없음 · 하루 1회(KST 00:00)</t>
         </is>
@@ -9714,210 +9854,210 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>1일차</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>att_moon_cactus</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>달빛 냥이 선인장</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>작은 소품</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2일차</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>att_stamp_calendar</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>출석 도장 달력</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>벽 꾸미기</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>3일차</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>att_pink_starlight</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>핑크 별 수면등</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>작은 소품</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>4일차</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>att_night_bunting</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>밤하늘 가랜드</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>벽 꾸미기</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>5일차</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>att_moon_globe</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>달빛 지구본</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>작은 소품</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>6일차</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>att_sakura_fishbowl</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>벚꽃 금붕어 어항</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>작은 소품</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>7일차</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>att_moon_cattower</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>달밤 캣타워</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>큰/테마 대표 가구</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
@@ -9945,7 +10085,7 @@
       <c r="F14" s="22" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>1일차</t>
         </is>
@@ -9953,10 +10093,10 @@
       <c r="B15" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>2일차</t>
         </is>
@@ -9964,10 +10104,10 @@
       <c r="B16" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>3일차</t>
         </is>
@@ -9975,10 +10115,10 @@
       <c r="B17" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>4일차</t>
         </is>
@@ -9986,10 +10126,10 @@
       <c r="B18" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>5일차</t>
         </is>
@@ -9997,10 +10137,10 @@
       <c r="B19" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>6일차</t>
         </is>
@@ -10008,32 +10148,32 @@
       <c r="B20" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>7일차</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr"/>
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>홀수 주기: 출석 선물 상자 / 짝수 주기: 확률업 뽑기권 1장 (mode)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>주간 포인트 합계</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B22" s="10">
         <f>SUM(B15:B20)</f>
         <v/>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" s="10" t="inlineStr"/>
     </row>
     <row r="23"/>
     <row r="24">
@@ -10069,163 +10209,163 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>상자</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>att_lav_moonlamp</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>라벤더 달 무드등</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>작은 소품</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>상자</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>att_rose_gramophone</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>로즈 축음기</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>작은 소품</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>상자</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>att_mint_yarnbasket</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>민트 털실 바구니</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>작은 소품</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>상자</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>att_lav_cushions</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>파스텔 방석 더미</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>작은 소품</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>상자</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>att_sky_catclock</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>하늘빛 냥이 벽시계</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>벽 꾸미기</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>다 모은 뒤</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr"/>
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>100 포인트로 대체</t>
         </is>
@@ -10265,64 +10405,64 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>30일</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>att_m30_goldneon</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>30일 골드 하트 네온</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>벽 꾸미기</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>badge_att_30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>100일</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>att_m100_nightlamp</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>100일 별밤 벽등</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>벽 꾸미기</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>badge_att_100</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>불가 · 출석 한정</t>
         </is>
@@ -10330,23 +10470,23 @@
     </row>
     <row r="35"/>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>30일 동안 받는 포인트(1주차 후 23일)</t>
         </is>
       </c>
-      <c r="B36">
+      <c r="B36" s="10">
         <f>B22*3+B15+B16</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>광고 포인트 하루 최대 100 대비 출석은 주 90 + 7일차 보너스</t>
         </is>
@@ -10457,7 +10597,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>도감에 등록됐어요! 토스 1원 받았어요</t>
+          <t>도감에 등록됐어요! 냥코인 1개 + 20포인트 받았어요</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
@@ -10526,6 +10666,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="17.15" customHeight="1" s="11">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -10533,6 +10674,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="11">
       <c r="A9" s="18" t="inlineStr">
         <is>
@@ -10668,7 +10810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="10" min="1" max="1"/>
@@ -10800,17 +10942,17 @@
     <row r="6" ht="17.15" customHeight="1" s="11">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>토스 지급 / 유저</t>
+          <t>냥코인 적립·출금 / 유저</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>1인당 누적 토스 지급</t>
+          <t>1인당 누적 냥코인 적립 / 토스포인트 출금</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>토스 지급 합 / 누적 유저</t>
+          <t>출금 합(원) / 누적 유저</t>
         </is>
       </c>
       <c r="D6" s="17" t="n"/>
@@ -10935,6 +11077,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="11">
       <c r="A13" s="13" t="inlineStr">
         <is>
@@ -10945,7 +11088,7 @@
     <row r="14" ht="17.15" customHeight="1" s="11">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>월간 카드팩: 새 카드 추가 시 economy.json tossPayout·도감 수 재계산</t>
+          <t>월간 카드팩: 새 카드 추가 시 economy.json nyangCoin.maxEarnPerUser·도감 수 재계산</t>
         </is>
       </c>
     </row>
@@ -10980,7 +11123,24 @@
     <row r="19" ht="17.15" customHeight="1" s="11">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>어뷰징 방지: 토스 1원은 토스 계정당 1회 서버 검증, 광고 보상은 광고 완료 콜백 후에만</t>
+          <t>어뷰징 방지: 냥코인 적립은 보상 id별 1회 서버 검증, 출금은 10 단위·requestId 멱등, 광고 보상은 광고 완료 콜백 후에만</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>출금 실패/보류율</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>failed+pending / 전체 출금 요청</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>서버 출금 기록</t>
         </is>
       </c>
     </row>

--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -527,7 +527,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -719,7 +718,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -790,7 +788,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="17.15" customHeight="1" s="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
@@ -818,7 +815,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="11">
       <c r="A14" s="18" t="inlineStr">
         <is>
@@ -881,7 +877,6 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="17.15" customHeight="1" s="11">
       <c r="A21" s="18" t="inlineStr">
         <is>
@@ -1095,7 +1090,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33" ht="17.15" customHeight="1" s="11">
       <c r="A33" s="13" t="inlineStr">
         <is>
@@ -1973,7 +1967,6 @@
         <v/>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -8216,7 +8209,6 @@
         </is>
       </c>
     </row>
-    <row r="148"/>
     <row r="149" ht="15" customHeight="1" s="11">
       <c r="A149" s="18" t="inlineStr">
         <is>
@@ -8417,7 +8409,6 @@
         <v/>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -8556,10 +8547,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12" ht="17.15" customHeight="1" s="11">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -8667,7 +8654,6 @@
         <v>400</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="17.15" customHeight="1" s="11">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -8713,7 +8699,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -8916,7 +8901,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="16.15" customHeight="1" s="11">
       <c r="A13" s="16" t="inlineStr">
         <is>
@@ -8990,7 +8974,6 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="17.15" customHeight="1" s="11">
       <c r="A21" s="14" t="inlineStr">
         <is>
@@ -9186,7 +9169,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -9807,7 +9789,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -9820,7 +9801,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -10063,7 +10043,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
@@ -10175,7 +10154,6 @@
       </c>
       <c r="C22" s="10" t="inlineStr"/>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
@@ -10371,7 +10349,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
@@ -10468,7 +10445,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
@@ -10503,7 +10479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="10" min="1" max="1"/>
@@ -10607,191 +10583,271 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="11">
-      <c r="A4" s="10" t="n">
-        <v>3</v>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>main→dex</t>
+          <t>draw-reveal</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>#icon-dex</t>
+          <t>#dex-toast</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>도감에서 모은 카드를 볼 수 있어요</t>
+          <t>냥코인을 처음 받았어요!</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>방금 뽑은 카드가 여기 들어갔어요</t>
+          <t>1냥코인 = 토스포인트 1원 · 카드·세트 완성으로 모여요 · 10개부터 보상함에서 받기 · 발바닥 포인트는 방꾸미기용</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>tap</t>
+          <t>tap 알겠어요</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17.15" customHeight="1" s="11">
       <c r="A5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>main→dex</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>#icon-dex</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>도감에서 모은 카드를 볼 수 있어요</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>방금 뽑은 카드가 여기 들어갔어요</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>room</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>#drawer-item-0</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>서랍에서 아이템을 꺼내 방에 놓아 보세요</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>다 꾸몄으면 완료를 눌러요</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>drag + tap 완료</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7" ht="17.15" customHeight="1" s="11">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>건너뛰기: 모든 단계 우상단 "건너뛰기", 보상은 그대로 지급. 1분 이내.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9" ht="15" customHeight="1" s="11">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>일차</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
+    <row r="7" ht="17.15" customHeight="1" s="11"/>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>건너뛰기: 우상단 "건너뛰기"(대상이 위쪽이면 말풍선 아래줄), 보상은 그대로 지급. 1분 이내.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="11"/>
+    <row r="10" ht="17.15" customHeight="1" s="11">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>보상함 튜토리얼 (상황형 1회: 냥코인 처음 10개 또는 보상함 처음 열기 중 먼저)</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>대상 요소</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>새 기능 말풍선 문구</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="17.15" customHeight="1" s="11">
-      <c r="A10" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>intro-extra-draws</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>#chip-draws</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>광고를 보면 하루 2번 더 뽑을 수 있어요</t>
-        </is>
-      </c>
-    </row>
     <row r="11" ht="17.15" customHeight="1" s="11">
-      <c r="A11" s="10" t="n">
-        <v>3</v>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>r1</t>
+        </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>intro-rateup</t>
+          <t>main</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>#btn-rateup</t>
+          <t>#icon-menu</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>확률업 뽑기가 열렸어요! 레어 이상이 더 잘 나와요</t>
+          <t>냥코인이 10개 모였어요!</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>메뉴를 열어 볼까요? (빨간 점)</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>tap</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17.15" customHeight="1" s="11">
-      <c r="A12" s="10" t="n">
-        <v>4</v>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>intro-paw-ads</t>
+          <t>menu</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>#btn-paw-ad</t>
+          <t>#menu-row-rewards</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>광고 보고 포인트 10개 받아요 (하루 10번까지)</t>
+          <t>냥코인이 10개 모였어요!</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>보상함에서 토스포인트로 받을 수 있어요</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>tap 보상함 열기</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="11">
-      <c r="A13" s="10" t="n">
-        <v>5</v>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>r3</t>
+        </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>intro-dup-convert</t>
+          <t>sheet:rewards</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>#dex-dup-convert</t>
+          <t>#wallet-card</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>겹친 카드는 포인트로 바꿀 수 있어요</t>
+          <t>내 냥코인은 여기 모여요</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>1냥코인은 토스포인트 1원이에요. 지금 {balance}냥코인 있어요</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>다음</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="11">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>r4</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>sheet:rewards</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>#withdraw-picker</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>10개 단위로 골라서 받아요</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>남는 {n}냥코인은 그대로 모여요 · 세트 보상은 모두 받기로 한 번에</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>알겠어요 (완료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>intro-cozy</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>#cozy-meter</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>아이템을 모을수록 아늑함 레벨이 올라가요</t>
         </is>
@@ -11077,7 +11133,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="11">
       <c r="A13" s="13" t="inlineStr">
         <is>

--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출석" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="튜토리얼" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="운영 지표" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="뽑기권" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'아이템 가격'!$A$3:$J$147</definedName>
@@ -162,7 +163,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -227,6 +228,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="10" min="1" max="1"/>
@@ -689,10 +693,335 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>뽑기권</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>확률업 뽑기권 200P, 주 7장·하루 2장, 보유 3장 공유 → 도감 중앙값 285→197일</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="11" min="1" max="1"/>
+    <col width="16" customWidth="1" style="11" min="2" max="2"/>
+    <col width="16" customWidth="1" style="11" min="3" max="3"/>
+    <col width="16" customWidth="1" style="11" min="4" max="4"/>
+    <col width="16" customWidth="1" style="11" min="5" max="5"/>
+    <col width="16" customWidth="1" style="11" min="6" max="6"/>
+    <col width="16" customWidth="1" style="11" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>포인트로 사는 확률업 뽑기권 (economy.json shop.tickets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="24" t="n"/>
+      <c r="E3" s="24" t="n"/>
+      <c r="F3" s="24" t="n"/>
+      <c r="G3" s="24" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>200 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>주간 한도</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7장 (월 00:00 KST 리셋)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>하루 한도</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2장</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>보유 한도</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3장 (출석 뽑기권과 공유)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>일반 뽑기권</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>넣지 않음 (짧은 광고 대체·방꾸미기 지연)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>서버: 잔액·주/일 한도·보유 한도, requestId 멱등, 한 트랜잭션</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>옵션 비교 (최대 참여 유저 4,000명, 도감 먼저 구매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>옵션</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>도감 p10</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>도감 중앙값</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>도감 p90</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>방꾸미기 완료 중앙값</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>방꾸미기 p90</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>1인 포인트 사용 중앙값</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>없음 (현재)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>197</v>
+      </c>
+      <c r="C13" t="n">
+        <v>285</v>
+      </c>
+      <c r="D13" t="n">
+        <v>436</v>
+      </c>
+      <c r="E13" t="n">
+        <v>144</v>
+      </c>
+      <c r="F13" t="n">
+        <v>147</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 300P · 주3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>166</v>
+      </c>
+      <c r="C14" t="n">
+        <v>243</v>
+      </c>
+      <c r="D14" t="n">
+        <v>368</v>
+      </c>
+      <c r="E14" t="n">
+        <v>246</v>
+      </c>
+      <c r="F14" t="n">
+        <v>278</v>
+      </c>
+      <c r="G14" t="n">
+        <v>31500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B 250P · 주5</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>151</v>
+      </c>
+      <c r="C15" t="n">
+        <v>219</v>
+      </c>
+      <c r="D15" t="n">
+        <v>333</v>
+      </c>
+      <c r="E15" t="n">
+        <v>272</v>
+      </c>
+      <c r="F15" t="n">
+        <v>345</v>
+      </c>
+      <c r="G15" t="n">
+        <v>39250</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C 200P · 주7 · 하루2 (채택)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>135</v>
+      </c>
+      <c r="C16" t="n">
+        <v>197</v>
+      </c>
+      <c r="D16" t="n">
+        <v>297</v>
+      </c>
+      <c r="E16" t="n">
+        <v>267</v>
+      </c>
+      <c r="F16" t="n">
+        <v>338</v>
+      </c>
+      <c r="G16" t="n">
+        <v>39600</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D A + 일반 120P 주7</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>146</v>
+      </c>
+      <c r="C17" t="n">
+        <v>213</v>
+      </c>
+      <c r="D17" t="n">
+        <v>329</v>
+      </c>
+      <c r="E17" t="n">
+        <v>317</v>
+      </c>
+      <c r="F17" t="n">
+        <v>421</v>
+      </c>
+      <c r="G17" t="n">
+        <v>52860</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E B + 일반 100P 주7</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>133</v>
+      </c>
+      <c r="C18" t="n">
+        <v>194</v>
+      </c>
+      <c r="D18" t="n">
+        <v>299</v>
+      </c>
+      <c r="E18" t="n">
+        <v>316</v>
+      </c>
+      <c r="F18" t="n">
+        <v>420</v>
+      </c>
+      <c r="G18" t="n">
+        <v>53400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="10" min="1" max="1"/>
@@ -702,6 +702,18 @@
       <c r="B17" s="10" t="inlineStr">
         <is>
           <t>확률업 뽑기권 200P, 주 7장·하루 2장, 보유 3장 공유 → 도감 중앙값 285→197일</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>보상 지급 방식</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>manual — 도감에서 직접 받기 (자동 적립 없음), 보상 id당 1회</t>
         </is>
       </c>
     </row>
@@ -755,72 +767,72 @@
       <c r="G3" s="24" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>200 포인트</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>주간 한도</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>7장 (월 00:00 KST 리셋)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>하루 한도</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>2장</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>보유 한도</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>3장 (출석 뽑기권과 공유)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>일반 뽑기권</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>넣지 않음 (짧은 광고 대체·방꾸미기 지연)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>검증</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>서버: 잔액·주/일 한도·보유 한도, requestId 멱등, 한 트랜잭션</t>
         </is>
@@ -871,152 +883,152 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>없음 (현재)</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="10" t="n">
         <v>197</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="10" t="n">
         <v>285</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="10" t="n">
         <v>436</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="10" t="n">
         <v>144</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="10" t="n">
         <v>147</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>A 300P · 주3</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="10" t="n">
         <v>166</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="10" t="n">
         <v>243</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="10" t="n">
         <v>368</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="10" t="n">
         <v>246</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="10" t="n">
         <v>278</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="10" t="n">
         <v>31500</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>B 250P · 주5</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="10" t="n">
         <v>151</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="10" t="n">
         <v>219</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="10" t="n">
         <v>333</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="10" t="n">
         <v>272</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="10" t="n">
         <v>345</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="10" t="n">
         <v>39250</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>C 200P · 주7 · 하루2 (채택)</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="10" t="n">
         <v>135</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="10" t="n">
         <v>197</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="10" t="n">
         <v>297</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="10" t="n">
         <v>267</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="10" t="n">
         <v>338</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="10" t="n">
         <v>39600</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>D A + 일반 120P 주7</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="10" t="n">
         <v>146</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="10" t="n">
         <v>213</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="10" t="n">
         <v>329</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="10" t="n">
         <v>317</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="10" t="n">
         <v>421</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="10" t="n">
         <v>52860</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>E B + 일반 100P 주7</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="10" t="n">
         <v>133</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="10" t="n">
         <v>194</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="10" t="n">
         <v>299</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="10" t="n">
         <v>316</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="10" t="n">
         <v>420</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="10" t="n">
         <v>53400</v>
       </c>
     </row>
@@ -10808,7 +10820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="10" min="1" max="1"/>
@@ -11179,6 +11191,23 @@
       <c r="D15" s="14" t="inlineStr">
         <is>
           <t>아이템을 모을수록 아늑함 레벨이 올라가요</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>도감 코인 배지</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>방금 만난 고양이가 선물을 들고 왔어요 / 코인을 톡 눌러 받아 보세요 → 받은 뒤 ncoin-intro</t>
         </is>
       </c>
     </row>

--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -706,12 +706,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>보상 지급 방식</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>manual — 도감에서 직접 받기 (자동 적립 없음), 보상 id당 1회</t>
         </is>
@@ -10820,7 +10820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="10" min="1" max="1"/>
@@ -11195,19 +11195,121 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>도감 코인 배지</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>방금 만난 고양이가 선물을 들고 왔어요 / 코인을 톡 눌러 받아 보세요 → 받은 뒤 ncoin-intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>뽑은 카드 칸 강조</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>방금 만난 고양이가 여기 들어왔어요 [다음]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>코인 배지 탭</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>코인을 톡 누르면 보상을 받아요 · 냥코인 1 + 20P</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>냥코인 소개</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>냥코인을 처음 받았어요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>서랍 아이템 집기</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>서랍에서 마음에 드는 아이템을 꼬옹 눌러 보세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>초록 칸으로 끌어 놓기</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>방으로 끌고 와서 초록 칸에 놓아 보세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>배치 성공</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>잘했어요! 다른 아이템도 자유롭게 꾸며 보세요 [완료]</t>
         </is>
       </c>
     </row>

--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="튜토리얼" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="운영 지표" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="뽑기권" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업적" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'아이템 가격'!$A$3:$J$147</definedName>
@@ -163,7 +164,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -231,6 +232,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,6 +533,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -749,6 +752,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
         <is>
@@ -838,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
@@ -1030,6 +1035,736 @@
       </c>
       <c r="G18" s="10" t="n">
         <v>53400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="C1" s="25" t="inlineStr">
+        <is>
+          <t>칭호</t>
+        </is>
+      </c>
+      <c r="D1" s="25" t="inlineStr">
+        <is>
+          <t>업적</t>
+        </is>
+      </c>
+      <c r="E1" s="25" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t>냥코인</t>
+        </is>
+      </c>
+      <c r="G1" s="25" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>first_meet</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>새내기 집사</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>첫 고양이 만나기</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>도감 1장</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>dex_10</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>골목 산책냥</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>도감 10장 모으기</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>도감 10장</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>dex_30</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>동네 고양이 반장</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>도감 30장 모으기</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>도감 30장</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>dex_60</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>냥덕 학자</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>도감 60장 모으기</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>도감 60장</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>dex_90</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>고양이 백과사전</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>도감 90장 모으기</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>도감 90장</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>first_5star</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>반짝별 수집가</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>5★ 카드 처음 만나기</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>5★ 1장</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>first_legend</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>전설을 본 냥이</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>레전드 카드 처음 만나기</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>레전드 1장</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>first_set</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>한 우물 집사</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>품종 세트 처음 완성</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>품종 세트 1개</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>draw_50</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>뽑기</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>행운 사냥꾼</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>카드 50번 뽑기</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>뽑기 50회</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>draw_300</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>뽑기</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>럭키 앞발</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>카드 300번 뽑기</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>뽑기 300회</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>draw_1000</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>뽑기</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>행운의 마스터냥</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>카드 1000번 뽑기</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>뽑기 1000회</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>att_7</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>출석</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>맨날 보고프냥</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>출석 7일</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>누적 출석 7일</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>att_30</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>출석</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>단골 집사</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>출석 30일</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>누적 출석 30일</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>att_100</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>출석</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>백일이냥</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>출석 100일</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>누적 출석 100일</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>room_10</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>방꾸미기</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>꾹꾹이 인테리어</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>가구·소품 10개 놓기</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>배치 10개 (동시)</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>room_30</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>방꾸미기</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>아늑함 장인</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>가구·소품 30개 놓기</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>배치 30개 (동시, 모든 방)</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>room_unlock2</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>방꾸미기</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>두 집 살림냥</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>두 번째 방 열기</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>방 2개 해금</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>room_all</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>방꾸미기</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>고양이 건축왕</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>모든 방 열기</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>방 전부 해금</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>exch_20</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>교환</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>알뜰 집사</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>중복 카드 20장 교환</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>교환 누적 20장</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>exch_100</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>교환</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>냥시장 큰손</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>중복 카드 100장 교환</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>교환 누적 100장</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr"/>
+      <c r="C22" s="10" t="inlineStr"/>
+      <c r="D22" s="10" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr"/>
+      <c r="F22" s="10">
+        <f>SUM(F2:F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="10">
+        <f>SUM(G2:G21)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1059,6 +1794,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1129,6 +1865,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="17.15" customHeight="1" s="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
@@ -1156,6 +1893,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="11">
       <c r="A14" s="18" t="inlineStr">
         <is>
@@ -1218,6 +1956,7 @@
         <v>150</v>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="17.15" customHeight="1" s="11">
       <c r="A21" s="18" t="inlineStr">
         <is>
@@ -1431,6 +2170,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="17.15" customHeight="1" s="11">
       <c r="A33" s="13" t="inlineStr">
         <is>
@@ -2308,6 +3048,7 @@
         <v/>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -8550,6 +9291,7 @@
         </is>
       </c>
     </row>
+    <row r="148"/>
     <row r="149" ht="15" customHeight="1" s="11">
       <c r="A149" s="18" t="inlineStr">
         <is>
@@ -8750,6 +9492,7 @@
         <v/>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -8888,6 +9631,10 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12" ht="17.15" customHeight="1" s="11">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -8995,6 +9742,7 @@
         <v>400</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="17.15" customHeight="1" s="11">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -9022,7 +9770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="48" customWidth="1" style="10" min="1" max="1"/>
@@ -9040,6 +9788,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -9075,11 +9824,11 @@
     <row r="4" ht="15" customHeight="1" s="11">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>새 카드 첫 획득</t>
+          <t>새 카드 1–3★</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="C4" s="17" t="n">
         <v>1</v>
@@ -9097,23 +9846,23 @@
       </c>
     </row>
     <row r="5" ht="17.15" customHeight="1" s="11">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>품종 1–5★ 완성</t>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>새 카드 4★</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="C5" s="17" t="n">
-        <v>10</v>
+      <c r="C5" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="D5" s="10">
         <f>B5*C5</f>
         <v/>
       </c>
-      <c r="E5" s="17" t="n">
-        <v>200</v>
+      <c r="E5" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="F5" s="10">
         <f>B5*E5</f>
@@ -9121,23 +9870,23 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="11">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>스페셜 세트 완성</t>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>새 카드 5★</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" s="10" t="n">
         <v>10</v>
       </c>
       <c r="D6" s="10">
         <f>B6*C6</f>
         <v/>
       </c>
-      <c r="E6" s="17" t="n">
-        <v>300</v>
+      <c r="E6" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="F6" s="10">
         <f>B6*E6</f>
@@ -9145,23 +9894,23 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="11">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>캐릭터 세트 완성</t>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>새 카드 밈(스페셜)</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="17" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="D7" s="10">
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="17" t="n">
-        <v>300</v>
+      <c r="E7" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="F7" s="10">
         <f>B7*E7</f>
@@ -9169,23 +9918,23 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="11">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>레전드 세트 완성</t>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>새 카드 캐릭터</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="D8" s="10">
         <f>B8*C8</f>
         <v/>
       </c>
-      <c r="E8" s="17" t="n">
-        <v>300</v>
+      <c r="E8" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="F8" s="10">
         <f>B8*E8</f>
@@ -9193,23 +9942,23 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="11">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>도감 전체 완성</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>새 카드 레전드</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="17" t="n">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="D9" s="10">
         <f>B9*C9</f>
         <v/>
       </c>
-      <c r="E9" s="17" t="n">
-        <v>3000</v>
+      <c r="E9" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="F9" s="10">
         <f>B9*E9</f>
@@ -9217,266 +9966,405 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="11">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="D10" s="13">
-        <f>SUM(D4:D9)</f>
-        <v/>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>품종 1–5★ 완성</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="10">
+        <f>B5*C5</f>
+        <v/>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>200</v>
       </c>
       <c r="F10" s="10">
-        <f>SUM(F4:F9)</f>
+        <f>B5*E5</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="17.15" customHeight="1" s="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>검증 (417냥코인이어야 해요)</t>
-        </is>
+          <t>스페셜 세트 완성</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>10</v>
       </c>
       <c r="D11" s="10">
-        <f>IF(D10=417,"OK","확인 필요")</f>
+        <f>B6*C6</f>
+        <v/>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="F11" s="10">
+        <f>B6*E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>캐릭터 세트 완성</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="10">
+        <f>B7*C7</f>
+        <v/>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="F12" s="10">
+        <f>B7*E7</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16.15" customHeight="1" s="11">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>광고 수익 손익분기</t>
-        </is>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>레전드 세트 완성</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="10">
+        <f>B8*C8</f>
+        <v/>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="F13" s="10">
+        <f>B8*E8</f>
+        <v/>
       </c>
     </row>
     <row r="14" ht="17.15" customHeight="1" s="11">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>도감 전체 완성</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" s="10">
+        <f>B9*C9</f>
+        <v/>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F14" s="10">
+        <f>B9*E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="17.15" customHeight="1" s="11">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>업적 (achievements.json)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="16" ht="17.15" customHeight="1" s="11">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="D16" s="13">
+        <f>SUM(D4:D15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="10">
+        <f>SUM(F4:F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="17.15" customHeight="1" s="11">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>검증 (988냥코인이어야 해요)</t>
+        </is>
+      </c>
+      <c r="D17" s="10">
+        <f>IF(D16=988,"OK","확인 필요")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="17.15" customHeight="1" s="11"/>
+    <row r="19" ht="17.15" customHeight="1" s="11">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>광고 수익 손익분기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
           <t>짧은 광고 eCPM (원)</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>앱인토스 대시보드에서 입력</t>
         </is>
-      </c>
-    </row>
-    <row r="15" ht="17.15" customHeight="1" s="11">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>긴 광고 eCPM (원)</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>앱인토스 대시보드에서 입력</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="17.15" customHeight="1" s="11">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>기간(일)</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" ht="17.15" customHeight="1" s="11">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>1인 하루 짧은 광고 수 (뽑기 3 + 포인트 8)</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" ht="17.15" customHeight="1" s="11">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>1인 하루 긴 광고 수</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="17.15" customHeight="1" s="11">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>기간 내 1인 냥코인 적립(=토스포인트 원, 시뮬 30일 중앙값)</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n">
-        <v>83</v>
       </c>
     </row>
     <row r="21" ht="17.15" customHeight="1" s="11">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>기간 내 1인 광고 수익(원)</t>
-        </is>
-      </c>
-      <c r="B21" s="10">
-        <f>IF(OR(B14="",B15=""),"eCPM 입력 필요",B16*(B17*B14+B18*B15)/1000)</f>
-        <v/>
+          <t>긴 광고 eCPM (원)</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>앱인토스 대시보드에서 입력</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="17.15" customHeight="1" s="11">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>1인 순이익(원) = 광고 수익 − 토스포인트 지급</t>
-        </is>
-      </c>
-      <c r="B22" s="10">
-        <f>IF(ISNUMBER(B21),B21-B19,"eCPM 입력 필요")</f>
-        <v/>
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>기간(일)</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="17.15" customHeight="1" s="11">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>손익분기 평균 eCPM (원, 모든 광고 동일 가정)</t>
-        </is>
-      </c>
-      <c r="B23" s="10">
-        <f>B19/(B16*(B17+B18)/1000)</f>
-        <v/>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>1인 하루 짧은 광고 수 (뽑기 3 + 포인트 8)</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="24" ht="17.15" customHeight="1" s="11">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>손익분기 짧은 광고 eCPM (긴 광고 eCPM 입력 시)</t>
-        </is>
-      </c>
-      <c r="B24" s="10">
-        <f>IF(B15="","긴 광고 eCPM 입력 필요",(B19*1000/B16-B18*B15)/B17)</f>
-        <v/>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>1인 하루 긴 광고 수</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="17.15" customHeight="1" s="11">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>최대 적립 417냥코인 회수에 필요한 광고 수 (평균 eCPM 입력 시)</t>
-        </is>
-      </c>
-      <c r="B25" s="10">
-        <f>IF(B14="","eCPM 입력 필요",417*1000/B14)</f>
-        <v/>
-      </c>
-    </row>
+          <t>기간 내 1인 냥코인 적립(=토스포인트 원, 시뮬 30일 중앙값)</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>토스포인트로 받기 (출금 규칙)</t>
-        </is>
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>기간 내 1인 광고 수익(원)</t>
+        </is>
+      </c>
+      <c r="B27" s="10">
+        <f>IF(OR(B14="",B15=""),"eCPM 입력 필요",B16*(B17*B14+B18*B15)/1000)</f>
+        <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>출금 단위</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="n">
-        <v>10</v>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>1인 순이익(원) = 광고 수익 − 토스포인트 지급</t>
+        </is>
+      </c>
+      <c r="B28" s="10">
+        <f>IF(ISNUMBER(B21),B21-B19,"eCPM 입력 필요")</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>최소 출금</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="n">
-        <v>10</v>
+          <t>손익분기 평균 eCPM (원, 모든 광고 동일 가정)</t>
+        </is>
+      </c>
+      <c r="B29" s="10">
+        <f>B19/(B16*(B17+B18)/1000)</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>1회 최대</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>floor(잔액/10)×10</t>
-        </is>
+          <t>손익분기 짧은 광고 eCPM (긴 광고 eCPM 입력 시)</t>
+        </is>
+      </c>
+      <c r="B30" s="10">
+        <f>IF(B15="","긴 광고 eCPM 입력 필요",(B19*1000/B16-B18*B15)/B17)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>남는 냥코인</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>그대로 보유 (예: 37 → 30 받고 7 남음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>검증</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>서버: 10의 배수 · 10 이상 · 잔액 이하 · 계정당 동시 1건</t>
-        </is>
-      </c>
-    </row>
+          <t>최대 적립냥코인 회수에 필요한 광고 수 (평균 eCPM 입력 시)</t>
+        </is>
+      </c>
+      <c r="B31" s="10">
+        <f>IF(B14="","eCPM 입력 필요",D16*1000/B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>멱등키</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>tossUserKey + withdrawRequestId</t>
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>토스포인트로 받기 (출금 규칙)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>지급</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>서버→서버 토스 포인트 지급 API 호출, 실패 시 잔액 복구</t>
-        </is>
+          <t>출금 단위</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>주의</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>지급 API 금액 한도·예산 충전·정책은 앱인토스 확인 필요</t>
-        </is>
+          <t>최소 출금</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>최대 적립 417 중 출금 가능</t>
-        </is>
-      </c>
-      <c r="B36" s="14">
-        <f>FLOOR(D10/10,1)*10</f>
+          <t>1회 최대</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>floor(잔액/10)×10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>남는 냥코인</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>그대로 보유 (예: 37 → 30 받고 7 남음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>서버: 10의 배수 · 10 이상 · 잔액 이하 · 계정당 동시 1건</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>멱등키</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>tossUserKey + withdrawRequestId</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>지급</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>서버→서버 토스 포인트 지급 API 호출, 실패 시 잔액 복구</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>지급 API 금액 한도·예산 충전·정책은 앱인토스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>최대 적립 중 출금 가능</t>
+        </is>
+      </c>
+      <c r="B42" s="14">
+        <f>FLOOR(D16/10,1)*10</f>
         <v/>
       </c>
     </row>
@@ -9510,6 +10398,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -10130,6 +11019,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -10142,6 +11032,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -10384,6 +11275,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
@@ -10495,6 +11387,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
@@ -10690,6 +11583,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
@@ -10786,6 +11680,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
@@ -11314,68 +12209,68 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>4-3 완료</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>→ 5단계로 이동</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>(tutorialDone은 5-3에서)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>5-1</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>메뉴 버튼</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>메뉴에서 모은 냥코인을 확인할 수 있어요</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>5-2</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>보상함 행</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>보상함을 눌러 보세요</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>5-3</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>지갑·출금 영역</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>냥코인 10개부터 토스포인트로 바꿀 수 있어요 · 하루 최대 50원 [알겠어요] → tutorialDone</t>
         </is>
@@ -11661,6 +12556,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="11">
       <c r="A13" s="13" t="inlineStr">
         <is>

--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -533,7 +533,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -752,7 +751,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
         <is>
@@ -842,7 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
@@ -1794,7 +1791,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1865,7 +1861,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="17.15" customHeight="1" s="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
@@ -1893,7 +1888,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="11">
       <c r="A14" s="18" t="inlineStr">
         <is>
@@ -1956,7 +1950,6 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="17.15" customHeight="1" s="11">
       <c r="A21" s="18" t="inlineStr">
         <is>
@@ -2170,7 +2163,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33" ht="17.15" customHeight="1" s="11">
       <c r="A33" s="13" t="inlineStr">
         <is>
@@ -3048,7 +3040,6 @@
         <v/>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -9291,7 +9282,6 @@
         </is>
       </c>
     </row>
-    <row r="148"/>
     <row r="149" ht="15" customHeight="1" s="11">
       <c r="A149" s="18" t="inlineStr">
         <is>
@@ -9492,7 +9482,6 @@
         <v/>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -9631,10 +9620,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12" ht="17.15" customHeight="1" s="11">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -9742,7 +9727,6 @@
         <v>400</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="17.15" customHeight="1" s="11">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -9770,7 +9754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="48" customWidth="1" style="10" min="1" max="1"/>
@@ -9788,7 +9772,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -10201,7 +10184,6 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
@@ -10257,7 +10239,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
@@ -10366,6 +10347,13 @@
       <c r="B42" s="14">
         <f>FLOOR(D16/10,1)*10</f>
         <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1.8: 출석 7일차 냥코인 추가로 1인 최대 지급은 고정되지 않아요 ('출석' 시트 참고)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -10398,7 +10386,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -11001,7 +10988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="11" min="1" max="1"/>
@@ -11019,7 +11006,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -11032,7 +11018,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -11275,7 +11260,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
@@ -11387,7 +11371,6 @@
       </c>
       <c r="C22" s="10" t="inlineStr"/>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
@@ -11583,7 +11566,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
@@ -11680,7 +11662,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
@@ -11701,6 +11682,218 @@
       <c r="B37" s="10" t="inlineStr">
         <is>
           <t>광고 포인트 하루 최대 100 대비 출석은 주 90 + 7일차 보너스</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>7일차 보너스 (1.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>냥코인</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>뽑기권</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>그냥 받기</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="n">
+        <v>100</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>기존 선물 상자/뽑기권에 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>30초 광고 보고</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" t="n">
+        <v>200</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>주기당 1회, 뽑기권 최대 3장</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>연간 냥코인 비용</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>주기 수</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>기본(원)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>광고(원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>매일 출석</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>50</v>
+      </c>
+      <c r="C45">
+        <f>B45*B41</f>
+        <v/>
+      </c>
+      <c r="D45">
+        <f>B45*B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>주 5일</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>35</v>
+      </c>
+      <c r="C46">
+        <f>B46*B41</f>
+        <v/>
+      </c>
+      <c r="D46">
+        <f>B46*B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>광고 1회 손익</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>eCPM</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>순수익(운영비30%)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>수수료15% 후</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>광고 시 지급 10원 대비</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C49">
+        <f>B50/1000*0.7</f>
+        <v/>
+      </c>
+      <c r="D49">
+        <f>C50*0.85</f>
+        <v/>
+      </c>
+      <c r="E49">
+        <f>C50-10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C50">
+        <f>B51/1000*0.7</f>
+        <v/>
+      </c>
+      <c r="D50">
+        <f>C51*0.85</f>
+        <v/>
+      </c>
+      <c r="E50">
+        <f>C51-10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>연간 상한 제안</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>300</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>초과분은 냥코인 1개당 10P</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12749,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="11">
       <c r="A13" s="13" t="inlineStr">
         <is>

--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="B22" s="19" t="n">
-        <v>0.345</v>
+        <v>0.372</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>0.15</v>
+        <v>0.193</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>10</v>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>0.285</v>
+        <v>0.3</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D23" s="10" t="n">
         <v>10</v>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="B25" s="19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>30</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>30</v>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D27" s="10" t="n">
         <v>60</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="B28" s="19" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="C28" s="19" t="n">
-        <v>0.045</v>
+        <v>0.025</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>60</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="B29" s="19" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="C29" s="19" t="n">
-        <v>0.025</v>
+        <v>0.012</v>
       </c>
       <c r="D29" s="10" t="n">
         <v>150</v>
@@ -2159,7 +2159,7 @@
     <row r="31" ht="17.15" customHeight="1" s="11">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>확률은 제안값이에요 (economy.json draws.rates_proposal). 확정 시 이 표와 서버 설정을 함께 바꿔요.</t>
+          <t>확률 확정 1.9 (옵션 B, economy.json draws.rates_proposal). 바꿀 때는 이 표와 서버 설정·확률 안내를 함께 바꿔요.</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10350,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>1.8: 출석 7일차 냥코인 추가로 1인 최대 지급은 고정되지 않아요 ('출석' 시트 참고)</t>
         </is>
@@ -11693,205 +11693,205 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>냥코인</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>포인트</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>뽑기권</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>그냥 받기</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>기존 선물 상자/뽑기권에 추가</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>30초 광고 보고</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>주기당 1회, 뽑기권 최대 3장</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>연간 냥코인 비용</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>주기 수</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>기본(원)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>광고(원)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>매일 출석</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="10">
         <f>B45*B41</f>
         <v/>
       </c>
-      <c r="D45">
+      <c r="D45" s="10">
         <f>B45*B42</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>주 5일</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="10">
         <f>B46*B41</f>
         <v/>
       </c>
-      <c r="D46">
+      <c r="D46" s="10">
         <f>B46*B42</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>광고 1회 손익</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>eCPM</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>순수익(운영비30%)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>수수료15% 후</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>광고 시 지급 10원 대비</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="n">
+      <c r="A49" s="10" t="inlineStr"/>
+      <c r="B49" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="10">
         <f>B50/1000*0.7</f>
         <v/>
       </c>
-      <c r="D49">
+      <c r="D49" s="10">
         <f>C50*0.85</f>
         <v/>
       </c>
-      <c r="E49">
+      <c r="E49" s="10">
         <f>C50-10</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="n">
+      <c r="A50" s="10" t="inlineStr"/>
+      <c r="B50" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="10">
         <f>B51/1000*0.7</f>
         <v/>
       </c>
-      <c r="D50">
+      <c r="D50" s="10">
         <f>C51*0.85</f>
         <v/>
       </c>
-      <c r="E50">
+      <c r="E50" s="10">
         <f>C51-10</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>연간 상한 제안</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>초과분은 냥코인 1개당 10P</t>
         </is>

--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="운영 지표" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="뽑기권" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업적" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="냥코인 지급처" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'아이템 가격'!$A$3:$J$147</definedName>
@@ -533,6 +534,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -751,6 +753,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
         <is>
@@ -840,6 +843,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
@@ -1761,6 +1765,312 @@
       </c>
       <c r="G22" s="10">
         <f>SUM(G2:G21)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" style="11" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>냥코인 지급처 (2.0) · 1냥코인 = 1원</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>지급처</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>양</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>한도</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>광고 뽑기</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>일반 광고 뽑기·광고 확률업 완료마다 (신규/중복 무관)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>하루 4 · 연 1,460</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ncoinSources.adDraw</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>새 카드 첫 획득</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1~50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1~3★ 1, 4★ 5, 5★ 10, 밈 5, 캐릭터 7, 레전드 50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>총 597</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>newCardFirstGet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>세트 완성</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>품종 18 + 스페셜·캐릭터·레전드 3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>총 210</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>setComplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>도감 전체 완성</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1회</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>setComplete.fullDex</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>업적</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>칭호별</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>achievements.json</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>총 81</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>achievements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>출석 7일차</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5 / 광고 10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8일차 이후 매 주기</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>연 250 / 500 (상한 꺼짐, 제안 300)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>day7Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>구매, 생애 첫 무료 뽑기, 뽑기권 뽑기, 포인트 광고</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>광고 뽑기 1회 마진</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>eCPM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>순수익(운영비 30%)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>−1냥코인</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>수수료 15% 후 −1냥코인</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C12">
+        <f>B12/1000*0.7</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>C12-1</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>C12*0.85-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C13">
+        <f>B13/1000*0.7</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>C13-1</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>C13*0.85-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C14">
+        <f>B14/1000*0.7</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>C14-1</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>C14*0.85-1</f>
         <v/>
       </c>
     </row>
@@ -1791,6 +2101,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1861,6 +2172,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="17.15" customHeight="1" s="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
@@ -1888,6 +2200,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="11">
       <c r="A14" s="18" t="inlineStr">
         <is>
@@ -1950,6 +2263,7 @@
         <v>150</v>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="17.15" customHeight="1" s="11">
       <c r="A21" s="18" t="inlineStr">
         <is>
@@ -2163,6 +2477,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="17.15" customHeight="1" s="11">
       <c r="A33" s="13" t="inlineStr">
         <is>
@@ -3040,6 +3355,7 @@
         <v/>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -9282,6 +9598,7 @@
         </is>
       </c>
     </row>
+    <row r="148"/>
     <row r="149" ht="15" customHeight="1" s="11">
       <c r="A149" s="18" t="inlineStr">
         <is>
@@ -9482,6 +9799,7 @@
         <v/>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -9620,6 +9938,10 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12" ht="17.15" customHeight="1" s="11">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -9727,6 +10049,7 @@
         <v>400</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="17.15" customHeight="1" s="11">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -9754,7 +10077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="48" customWidth="1" style="10" min="1" max="1"/>
@@ -9772,6 +10095,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -10184,6 +10508,7 @@
         <v>83</v>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
@@ -10239,6 +10564,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
@@ -10349,10 +10675,18 @@
         <v/>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
           <t>1.8: 출석 7일차 냥코인 추가로 1인 최대 지급은 고정되지 않아요 ('출석' 시트 참고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2.0: 광고 뽑기 1회마다 +1냥코인 ('냥코인 지급처' 시트)</t>
         </is>
       </c>
     </row>
@@ -10386,6 +10720,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -11006,6 +11341,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -11018,6 +11354,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -11260,6 +11597,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
@@ -11371,6 +11709,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
@@ -11566,6 +11905,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
@@ -11662,6 +12002,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
@@ -11685,6 +12026,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
         <is>
@@ -11761,6 +12103,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
@@ -11819,6 +12162,7 @@
         <v/>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
@@ -12749,6 +13093,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="11">
       <c r="A13" s="13" t="inlineStr">
         <is>

--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -534,7 +534,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -753,7 +752,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
         <is>
@@ -843,7 +841,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
@@ -1779,7 +1776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" style="11" min="3" max="3"/>
@@ -1788,290 +1785,321 @@
     <row r="1">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>냥코인 지급처 (2.0) · 1냥코인 = 1원</t>
+          <t>냥코인 지급처 (2.1) · 1냥코인 = 1원</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>지급처</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>양</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>조건</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>한도</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>광고 뽑기</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>일반 광고 뽑기·광고 확률업 완료마다 (신규/중복 무관)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>하루 4 · 연 1,460</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>ncoinSources.adDraw</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>포인트 광고</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>포인트 광고(10P) 완료마다 (주말에도 1개)</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>하루 10 · 연 3,650</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>ncoinSources.adPaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>새 카드 첫 획득</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>1~50</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>1~3★ 1, 4★ 5, 5★ 10, 밈 5, 캐릭터 7, 레전드 50</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>총 597</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>newCardFirstGet</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>세트 완성</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>품종 18 + 스페셜·캐릭터·레전드 3</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>총 210</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>setComplete</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>도감 전체 완성</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>1회</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>setComplete.fullDex</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>업적</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>칭호별</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>achievements.json</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>총 81</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>achievements.json</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>출석 7일차</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>5 / 광고 10</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>8일차 이후 매 주기</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>연 250 / 500 (상한 꺼짐, 제안 300)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>day7Bonus</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>구매, 생애 첫 무료 뽑기, 뽑기권 뽑기, 포인트 광고</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>광고 뽑기 1회 마진</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>구매, 생애 첫 무료 뽑기, 뽑기권 뽑기</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>광고 1회 마진 (뽑기·포인트 광고 공통)</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>eCPM</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>순수익(운영비 30%)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>−1냥코인</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>수수료 15% 후 −1냥코인</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="n">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr"/>
+      <c r="B13" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="C12">
-        <f>B12/1000*0.7</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>C12-1</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>C12*0.85-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="n">
+      <c r="C13" s="10">
+        <f>B13/1000*0.7</f>
+        <v/>
+      </c>
+      <c r="D13" s="10">
+        <f>C13-1</f>
+        <v/>
+      </c>
+      <c r="E13" s="10">
+        <f>C13*0.85-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr"/>
+      <c r="B14" s="10" t="n">
         <v>14000</v>
       </c>
-      <c r="C13">
-        <f>B13/1000*0.7</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>C13-1</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>C13*0.85-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="n">
+      <c r="C14" s="10">
+        <f>B14/1000*0.7</f>
+        <v/>
+      </c>
+      <c r="D14" s="10">
+        <f>C14-1</f>
+        <v/>
+      </c>
+      <c r="E14" s="10">
+        <f>C14*0.85-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr"/>
+      <c r="B15" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="C14">
-        <f>B14/1000*0.7</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>C14-1</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>C14*0.85-1</f>
-        <v/>
+      <c r="C15" s="10">
+        <f>B15/1000*0.7</f>
+        <v/>
+      </c>
+      <c r="D15" s="10">
+        <f>C15-1</f>
+        <v/>
+      </c>
+      <c r="E15" s="10">
+        <f>C15*0.85-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>광고 냥코인 하루 최대 14 (뽑기 4 + 포인트 광고 10)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2101,7 +2129,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -2172,7 +2199,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="17.15" customHeight="1" s="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
@@ -2200,7 +2226,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="11">
       <c r="A14" s="18" t="inlineStr">
         <is>
@@ -2263,7 +2288,6 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="17.15" customHeight="1" s="11">
       <c r="A21" s="18" t="inlineStr">
         <is>
@@ -2477,7 +2501,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33" ht="17.15" customHeight="1" s="11">
       <c r="A33" s="13" t="inlineStr">
         <is>
@@ -3355,7 +3378,6 @@
         <v/>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -9598,7 +9620,6 @@
         </is>
       </c>
     </row>
-    <row r="148"/>
     <row r="149" ht="15" customHeight="1" s="11">
       <c r="A149" s="18" t="inlineStr">
         <is>
@@ -9799,7 +9820,6 @@
         <v/>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -9938,10 +9958,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12" ht="17.15" customHeight="1" s="11">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -10049,7 +10065,6 @@
         <v>400</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="17.15" customHeight="1" s="11">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -10095,7 +10110,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -10508,7 +10522,6 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
@@ -10564,7 +10577,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
@@ -10675,7 +10687,6 @@
         <v/>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
@@ -10684,7 +10695,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>2.0: 광고 뽑기 1회마다 +1냥코인 ('냥코인 지급처' 시트)</t>
         </is>
@@ -10720,7 +10731,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -11341,7 +11351,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -11354,7 +11363,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -11597,7 +11605,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
@@ -11709,7 +11716,6 @@
       </c>
       <c r="C22" s="10" t="inlineStr"/>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
@@ -11905,7 +11911,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
@@ -12002,7 +12007,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
@@ -12026,7 +12030,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
         <is>
@@ -12103,7 +12106,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
@@ -12162,7 +12164,6 @@
         <v/>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
@@ -13093,7 +13094,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="11">
       <c r="A13" s="13" t="inlineStr">
         <is>

--- a/config/LuckyCat-economy.xlsx
+++ b/config/LuckyCat-economy.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="뽑기권" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업적" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="냥코인 지급처" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="코지 점수" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'아이템 가격'!$A$3:$J$147</definedName>
@@ -2107,6 +2108,179 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>코지 점수 (2.2) · 배치 여부 무관</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1개째</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2개째부터(50% 올림)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>최대 보유</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>작은 소품</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <f>ROUNDUP(B3*0.5,0)</f>
+        <v/>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>일반 가구</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <f>ROUNDUP(B4*0.5,0)</f>
+        <v/>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>큰/테마 대표</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <f>ROUNDUP(B5*0.5,0)</f>
+        <v/>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>벽 꾸미기</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <f>ROUNDUP(B6*0.5,0)</f>
+        <v/>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>벽지/바닥</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>중복 없음</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>레전드급</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <f>ROUNDUP(B8*0.5,0)</f>
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>출석 한정</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>등급대로</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>중복 없음</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>레벨 속도: 중복은 점수/가격이 새 아이템보다 낮아 Lv5·Lv8 도달일 변화 없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
